--- a/Seva/22_19252.xlsx
+++ b/Seva/22_19252.xlsx
@@ -1,17 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11008"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/work/lessons/inf/ege-info/Seva/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{811856B6-5F06-4540-95DD-8FC8C5A92A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7725"/>
+    <workbookView xWindow="17280" yWindow="760" windowWidth="17280" windowHeight="20100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="125725"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -48,8 +54,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -356,23 +362,23 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -383,7 +389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>101</v>
       </c>
@@ -394,7 +400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>102</v>
       </c>
@@ -405,7 +411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>103</v>
       </c>
@@ -416,7 +422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>104</v>
       </c>
@@ -427,7 +433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>105</v>
       </c>
@@ -438,7 +444,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>106</v>
       </c>
@@ -449,7 +455,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>107</v>
       </c>
@@ -460,7 +466,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>108</v>
       </c>
@@ -471,7 +477,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>109</v>
       </c>
@@ -482,7 +488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>110</v>
       </c>
@@ -493,7 +499,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>111</v>
       </c>
@@ -504,7 +510,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>112</v>
       </c>
@@ -515,7 +521,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>113</v>
       </c>
@@ -526,7 +532,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>114</v>
       </c>
@@ -537,7 +543,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>115</v>
       </c>
@@ -548,7 +554,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>116</v>
       </c>
@@ -559,7 +565,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>117</v>
       </c>
